--- a/docs/detail-design/17_CaiDat.xlsx
+++ b/docs/detail-design/17_CaiDat.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="177">
   <si>
     <t>SWEET HOME · DETAIL DESIGN · CÀI ĐẶT</t>
   </si>
@@ -46,7 +46,7 @@
     <t>File này mô tả</t>
   </si>
   <si>
-    <t>Tab Mẫu tin nhắn: danh sách mẫu, thêm/sửa/xoá mẫu, chọn mẫu tự chọn sẵn cho từng hình thức check-in, chèn biến vào nội dung. Tab Thông tin homestay: tên, hotline, địa chỉ, link bản đồ, wifi — dùng cho biến trong tin nhắn. Nhân viên chỉ xem.</t>
+    <t>Tab Mẫu tin nhắn: danh sách mẫu, thêm/sửa/xoá mẫu, chọn mẫu tự chọn sẵn cho từng hình thức check-in, chèn biến vào nội dung, xem trước với đơn mẫu (che mã cửa). Tab Thông tin homestay: tên, hotline, địa chỉ, link bản đồ, wifi — dùng cho biến trong tin nhắn. Nhân viên chỉ xem.</t>
   </si>
   <si>
     <t>Cách đi đến</t>
@@ -134,6 +134,12 @@
     <t>Tạo mới.</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Thêm khung "Xem trước với đơn mẫu" (che mã cửa); ô thiếu viền đỏ + hộp lỗi khi lưu; giới hạn độ dài ô chữ.</t>
+  </si>
+  <si>
     <t>Ảnh 1. Tab Mẫu tin nhắn (Quản lý)</t>
   </si>
   <si>
@@ -278,6 +284,18 @@
     <t>Bấm để chèn {biến} vào vị trí con trỏ trong Nội dung. Nút "Mã cửa" tô màu cảnh báo (nhạy cảm): mẫu có mã cửa, mỗi lần sao chép được ghi nhật ký. Danh sách biến: xem sheet 4.</t>
   </si>
   <si>
+    <t>Xem trước với đơn mẫu SH-1036</t>
+  </si>
+  <si>
+    <t>Khung chữ (chỉ đọc)</t>
+  </si>
+  <si>
+    <t>previewParts() · buildSampleMessageContext()</t>
+  </si>
+  <si>
+    <t>Nội dung đang gõ ghép với một đơn mẫu cố định (Phạm Quốc Bảo, phòng 101 · Mộc, qua đêm…) + thông tin homestay đã lưu; cập nhật ngay khi gõ, giữ xuống dòng. {ma_cua} hiện "●●●●●● (hiện khi sao chép)" màu nhạt. Ẩn khi nội dung trống. Không gọi API đơn, không ghi nhật ký; Nhân viên cũng thấy.</t>
+  </si>
+  <si>
     <t>Xoá mẫu · Huỷ · Lưu mẫu</t>
   </si>
   <si>
@@ -401,7 +419,7 @@
     <t>2. Mẫu tin nhắn</t>
   </si>
   <si>
-    <t>Lưu: form thiếu tên / nội dung → không gửi. POST /api/message-templates hoặc PUT /api/message-templates/{id} { name, body, defaultForCheckInMode }.</t>
+    <t>Lưu: form thiếu tên / nội dung → ô viền đỏ, hộp lỗi "Vui lòng nhập đủ các ô bắt buộc (viền đỏ).", không gửi. POST /api/message-templates hoặc PUT /api/message-templates/{id} { name, body, defaultForCheckInMode }.</t>
   </si>
   <si>
     <t>Backend: chọn mặc định cho một hình thức → mẫu khác đang mặc định cho hình thức đó tự về NULL (mỗi hình thức tối đa 1 mẫu).</t>
@@ -416,7 +434,13 @@
     <t>4.</t>
   </si>
   <si>
-    <t>Không ghi nhật ký thao tác (cấu hình). Lỗi: 404 "Mẫu tin nhắn không tồn tại"; 400 "Dữ liệu không hợp lệ" (thiếu tên/nội dung khi gọi thẳng API).</t>
+    <t>Không ghi nhật ký thao tác (cấu hình). Lỗi: 404 "Mẫu tin nhắn không tồn tại"; 400 "Dữ liệu không hợp lệ" (thiếu tên/nội dung, tên &gt; 100 hoặc nội dung &gt; 2000 ký tự khi gọi thẳng API — errors.{trường} "Tối đa N ký tự").</t>
+  </si>
+  <si>
+    <t>5.</t>
+  </si>
+  <si>
+    <t>Xem trước (frontend): renderMessageTemplate(nội dung, buildSampleMessageContext(homestay đã lưu, ký tự đánh dấu)) rồi tách theo ký tự đánh dấu của {ma_cua} để chèn chữ che vào giữa — mã cửa thật không bao giờ được lấy ở màn này.</t>
   </si>
   <si>
     <t>3. Biến dùng trong nội dung</t>
@@ -521,20 +545,17 @@
     <t>4. Thông tin homestay</t>
   </si>
   <si>
-    <t>Lưu: thiếu tên / hotline / địa chỉ → không gửi. PUT /api/settings/homestay { name, hotline, address, mapLink, wifiName, wifiPassword } (ô trống tuỳ chọn gửi null).</t>
+    <t>Lưu: thiếu tên / hotline / địa chỉ → ô viền đỏ, hộp lỗi "Vui lòng nhập đủ các ô bắt buộc (viền đỏ).", không gửi. PUT /api/settings/homestay { name, hotline, address, mapLink, wifiName, wifiPassword } (ô trống tuỳ chọn gửi null).</t>
   </si>
   <si>
     <t>Không ghi nhật ký thao tác. Lỗi khác: "Không lưu được thông tin, thử lại sau."</t>
-  </si>
-  <si>
-    <t>Khác thiết kế ban đầu (screens.md, business-rules.md): màn chưa có phần "xem trước" nội dung mẫu (che mã cửa) — đã báo lại để xem xét.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -566,12 +587,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF64748B"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -626,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -650,9 +665,6 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -681,7 +693,7 @@
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9658350" cy="8041917"/>
+    <xdr:ext cx="9658350" cy="10054074"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -717,7 +729,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9658350" cy="6036468"/>
@@ -756,7 +768,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>92</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9658350" cy="6036468"/>
@@ -1119,7 +1131,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG21"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1314,7 +1326,7 @@
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
     </row>
-    <row r="6" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="6" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
@@ -1850,8 +1862,50 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
+    <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:AG2"/>
@@ -1891,6 +1945,10 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:M21"/>
     <mergeCell ref="N21:AG21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -1901,7 +1959,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG82"/>
+  <dimension ref="B1:AG92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1910,7 +1968,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -1944,83 +2002,83 @@
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
     </row>
-    <row r="47" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B47" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-      <c r="Q47" s="4"/>
-      <c r="R47" s="4"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
-      <c r="V47" s="4"/>
-      <c r="W47" s="4"/>
-      <c r="X47" s="4"/>
-      <c r="Y47" s="4"/>
-      <c r="Z47" s="4"/>
-      <c r="AA47" s="4"/>
-      <c r="AB47" s="4"/>
-      <c r="AC47" s="4"/>
-      <c r="AD47" s="4"/>
-      <c r="AE47" s="4"/>
-      <c r="AF47" s="4"/>
-      <c r="AG47" s="4"/>
-    </row>
-    <row r="82" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B82" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="4"/>
-      <c r="M82" s="4"/>
-      <c r="N82" s="4"/>
-      <c r="O82" s="4"/>
-      <c r="P82" s="4"/>
-      <c r="Q82" s="4"/>
-      <c r="R82" s="4"/>
-      <c r="S82" s="4"/>
-      <c r="T82" s="4"/>
-      <c r="U82" s="4"/>
-      <c r="V82" s="4"/>
-      <c r="W82" s="4"/>
-      <c r="X82" s="4"/>
-      <c r="Y82" s="4"/>
-      <c r="Z82" s="4"/>
-      <c r="AA82" s="4"/>
-      <c r="AB82" s="4"/>
-      <c r="AC82" s="4"/>
-      <c r="AD82" s="4"/>
-      <c r="AE82" s="4"/>
-      <c r="AF82" s="4"/>
-      <c r="AG82" s="4"/>
+    <row r="57" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B57" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
+      <c r="AB57" s="4"/>
+      <c r="AC57" s="4"/>
+      <c r="AD57" s="4"/>
+      <c r="AE57" s="4"/>
+      <c r="AF57" s="4"/>
+      <c r="AG57" s="4"/>
+    </row>
+    <row r="92" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B92" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C92" s="4"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="4"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="4"/>
+      <c r="Q92" s="4"/>
+      <c r="R92" s="4"/>
+      <c r="S92" s="4"/>
+      <c r="T92" s="4"/>
+      <c r="U92" s="4"/>
+      <c r="V92" s="4"/>
+      <c r="W92" s="4"/>
+      <c r="X92" s="4"/>
+      <c r="Y92" s="4"/>
+      <c r="Z92" s="4"/>
+      <c r="AA92" s="4"/>
+      <c r="AB92" s="4"/>
+      <c r="AC92" s="4"/>
+      <c r="AD92" s="4"/>
+      <c r="AE92" s="4"/>
+      <c r="AF92" s="4"/>
+      <c r="AG92" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:AG1"/>
-    <mergeCell ref="B47:AG47"/>
-    <mergeCell ref="B82:AG82"/>
+    <mergeCell ref="B57:AG57"/>
+    <mergeCell ref="B92:AG92"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>
@@ -2032,7 +2090,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG25"/>
+  <dimension ref="B1:AG26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2041,7 +2099,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2077,10 +2135,10 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -2091,22 +2149,22 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -2114,12 +2172,12 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -2132,33 +2190,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -2166,12 +2224,12 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -2184,33 +2242,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -2218,12 +2276,12 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -2236,33 +2294,33 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -2270,12 +2328,12 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -2288,33 +2346,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -2322,12 +2380,12 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -2340,33 +2398,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -2374,12 +2432,12 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -2392,33 +2450,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -2426,12 +2484,12 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -2450,27 +2508,27 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -2478,12 +2536,12 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -2496,33 +2554,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -2530,12 +2588,12 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -2543,38 +2601,38 @@
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
     </row>
-    <row r="11" ht="95" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="11" ht="147" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="6">
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -2582,12 +2640,12 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -2595,178 +2653,178 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
     </row>
-    <row r="13" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
-      <c r="AE13" s="4"/>
-      <c r="AF13" s="4"/>
-      <c r="AG13" s="4"/>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
+    <row r="12" ht="95" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+    </row>
+    <row r="14" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="4"/>
+      <c r="AF14" s="4"/>
+      <c r="AG14" s="4"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5" t="s">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5" t="s">
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5" t="s">
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Z14" s="5"/>
-      <c r="AA14" s="5"/>
-      <c r="AB14" s="5" t="s">
+      <c r="R15" s="5"/>
+      <c r="S15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AC14" s="5"/>
-      <c r="AD14" s="5"/>
-      <c r="AE14" s="5"/>
-      <c r="AF14" s="5"/>
-      <c r="AG14" s="5"/>
-    </row>
-    <row r="15" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B15" s="6">
-        <v>10</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="3"/>
-      <c r="AF15" s="3"/>
-      <c r="AG15" s="3"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="5"/>
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="6">
         <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -2774,12 +2832,12 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -2792,33 +2850,33 @@
         <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -2826,12 +2884,12 @@
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -2839,38 +2897,38 @@
       <c r="AF17" s="3"/>
       <c r="AG17" s="3"/>
     </row>
-    <row r="18" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="6">
         <v>13</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="R18" s="3"/>
       <c r="S18" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
@@ -2878,12 +2936,12 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -2891,38 +2949,38 @@
       <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
     </row>
-    <row r="19" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="19" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="6">
         <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="R19" s="3"/>
       <c r="S19" s="3" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -2930,12 +2988,12 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -2943,38 +3001,38 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
     </row>
-    <row r="20" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="6">
         <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="R20" s="3"/>
       <c r="S20" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -2982,12 +3040,12 @@
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -2995,38 +3053,38 @@
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
     </row>
-    <row r="21" ht="69" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="21" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="6">
         <v>16</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="P21" s="3"/>
       <c r="Q21" s="3" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
       <c r="R21" s="3"/>
       <c r="S21" s="3" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
@@ -3034,12 +3092,12 @@
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
       <c r="AB21" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
@@ -3047,148 +3105,200 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
-    <row r="23" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
-      <c r="Y23" s="4"/>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="4"/>
-      <c r="AB23" s="4"/>
-      <c r="AC23" s="4"/>
-      <c r="AD23" s="4"/>
-      <c r="AE23" s="4"/>
-      <c r="AF23" s="4"/>
-      <c r="AG23" s="4"/>
-    </row>
-    <row r="24" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="5" t="s">
+    <row r="22" ht="69" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="6">
+        <v>17</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
+    <row r="24" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5" t="s">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
+      <c r="AB24" s="4"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4"/>
+      <c r="AF24" s="4"/>
+      <c r="AG24" s="4"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5" t="s">
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5" t="s">
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5" t="s">
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Z24" s="5"/>
-      <c r="AA24" s="5"/>
-      <c r="AB24" s="5" t="s">
+      <c r="R25" s="5"/>
+      <c r="S25" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AC24" s="5"/>
-      <c r="AD24" s="5"/>
-      <c r="AE24" s="5"/>
-      <c r="AF24" s="5"/>
-      <c r="AG24" s="5"/>
-    </row>
-    <row r="25" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B25" s="6">
-        <v>17</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z25" s="3"/>
-      <c r="AA25" s="3"/>
-      <c r="AB25" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC25" s="3"/>
-      <c r="AD25" s="3"/>
-      <c r="AE25" s="3"/>
-      <c r="AF25" s="3"/>
-      <c r="AG25" s="3"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z25" s="5"/>
+      <c r="AA25" s="5"/>
+      <c r="AB25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC25" s="5"/>
+      <c r="AD25" s="5"/>
+      <c r="AE25" s="5"/>
+      <c r="AF25" s="5"/>
+      <c r="AG25" s="5"/>
+    </row>
+    <row r="26" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B26" s="6">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="163">
+  <mergeCells count="171">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -3270,15 +3380,15 @@
     <mergeCell ref="S11:X11"/>
     <mergeCell ref="Y11:AA11"/>
     <mergeCell ref="AB11:AG11"/>
-    <mergeCell ref="B13:AG13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="S14:X14"/>
-    <mergeCell ref="Y14:AA14"/>
-    <mergeCell ref="AB14:AG14"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="S12:X12"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB12:AG12"/>
+    <mergeCell ref="B14:AG14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="J15:N15"/>
@@ -3335,15 +3445,15 @@
     <mergeCell ref="S21:X21"/>
     <mergeCell ref="Y21:AA21"/>
     <mergeCell ref="AB21:AG21"/>
-    <mergeCell ref="B23:AG23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:N24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="S24:X24"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="AB24:AG24"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:N22"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="S22:X22"/>
+    <mergeCell ref="Y22:AA22"/>
+    <mergeCell ref="AB22:AG22"/>
+    <mergeCell ref="B24:AG24"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="G25:I25"/>
     <mergeCell ref="J25:N25"/>
@@ -3352,6 +3462,14 @@
     <mergeCell ref="S25:X25"/>
     <mergeCell ref="Y25:AA25"/>
     <mergeCell ref="AB25:AG25"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:N26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="S26:X26"/>
+    <mergeCell ref="Y26:AA26"/>
+    <mergeCell ref="AB26:AG26"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -3371,7 +3489,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3407,7 +3525,7 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -3443,10 +3561,10 @@
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -3481,10 +3599,10 @@
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -3519,7 +3637,7 @@
     </row>
     <row r="6" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -3553,12 +3671,12 @@
       <c r="AF6" s="4"/>
       <c r="AG6" s="4"/>
     </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="7" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -3593,10 +3711,10 @@
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -3631,10 +3749,10 @@
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -3667,12 +3785,12 @@
       <c r="AF9" s="8"/>
       <c r="AG9" s="8"/>
     </row>
-    <row r="10" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="10" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -3705,125 +3823,123 @@
       <c r="AF10" s="8"/>
       <c r="AG10" s="8"/>
     </row>
-    <row r="12" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
-      <c r="AB12" s="4"/>
-      <c r="AC12" s="4"/>
-      <c r="AD12" s="4"/>
-      <c r="AE12" s="4"/>
-      <c r="AF12" s="4"/>
-      <c r="AG12" s="4"/>
-    </row>
-    <row r="13" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
-      <c r="Z13" s="5"/>
-      <c r="AA13" s="5"/>
-      <c r="AB13" s="5"/>
-      <c r="AC13" s="5"/>
-      <c r="AD13" s="5"/>
-      <c r="AE13" s="5"/>
-      <c r="AF13" s="5"/>
-      <c r="AG13" s="5"/>
+    <row r="11" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8"/>
+      <c r="AA11" s="8"/>
+      <c r="AB11" s="8"/>
+      <c r="AC11" s="8"/>
+      <c r="AD11" s="8"/>
+      <c r="AE11" s="8"/>
+      <c r="AF11" s="8"/>
+      <c r="AG11" s="8"/>
+    </row>
+    <row r="13" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="4"/>
+      <c r="AE13" s="4"/>
+      <c r="AF13" s="4"/>
+      <c r="AG13" s="4"/>
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="3"/>
-      <c r="AG14" s="3"/>
+      <c r="B14" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="5"/>
+      <c r="AB14" s="5"/>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="5"/>
+      <c r="AE14" s="5"/>
+      <c r="AF14" s="5"/>
+      <c r="AG14" s="5"/>
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -3832,7 +3948,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -3840,7 +3956,7 @@
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
@@ -3863,7 +3979,7 @@
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -3872,7 +3988,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -3880,7 +3996,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -3903,7 +4019,7 @@
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -3912,7 +4028,7 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -3920,7 +4036,7 @@
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
@@ -3943,7 +4059,7 @@
     </row>
     <row r="18" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -3952,7 +4068,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -3960,7 +4076,7 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
@@ -3983,7 +4099,7 @@
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -3992,7 +4108,7 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -4000,7 +4116,7 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
@@ -4021,9 +4137,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
     </row>
-    <row r="20" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -4032,7 +4148,7 @@
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -4040,7 +4156,7 @@
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
@@ -4061,9 +4177,9 @@
       <c r="AF20" s="3"/>
       <c r="AG20" s="3"/>
     </row>
-    <row r="21" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="21" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -4072,7 +4188,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -4080,7 +4196,7 @@
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
@@ -4103,7 +4219,7 @@
     </row>
     <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -4112,7 +4228,7 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -4120,7 +4236,7 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
@@ -4141,9 +4257,9 @@
       <c r="AF22" s="3"/>
       <c r="AG22" s="3"/>
     </row>
-    <row r="23" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -4152,7 +4268,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
@@ -4160,7 +4276,7 @@
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
@@ -4181,86 +4297,88 @@
       <c r="AF23" s="3"/>
       <c r="AG23" s="3"/>
     </row>
-    <row r="25" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B25" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
-      <c r="Z25" s="4"/>
-      <c r="AA25" s="4"/>
-      <c r="AB25" s="4"/>
-      <c r="AC25" s="4"/>
-      <c r="AD25" s="4"/>
-      <c r="AE25" s="4"/>
-      <c r="AF25" s="4"/>
-      <c r="AG25" s="4"/>
-    </row>
-    <row r="26" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="8"/>
-      <c r="Z26" s="8"/>
-      <c r="AA26" s="8"/>
-      <c r="AB26" s="8"/>
-      <c r="AC26" s="8"/>
-      <c r="AD26" s="8"/>
-      <c r="AE26" s="8"/>
-      <c r="AF26" s="8"/>
-      <c r="AG26" s="8"/>
-    </row>
-    <row r="27" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="24" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+    </row>
+    <row r="26" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
+      <c r="AF26" s="4"/>
+      <c r="AG26" s="4"/>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -4294,40 +4412,42 @@
       <c r="AG27" s="8"/>
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B28" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="9"/>
-      <c r="AE28" s="9"/>
-      <c r="AF28" s="9"/>
-      <c r="AG28" s="9"/>
+      <c r="B28" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="8"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="8"/>
+      <c r="Z28" s="8"/>
+      <c r="AA28" s="8"/>
+      <c r="AB28" s="8"/>
+      <c r="AC28" s="8"/>
+      <c r="AD28" s="8"/>
+      <c r="AE28" s="8"/>
+      <c r="AF28" s="8"/>
+      <c r="AG28" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="47">
@@ -4340,10 +4460,8 @@
     <mergeCell ref="C8:AG8"/>
     <mergeCell ref="C9:AG9"/>
     <mergeCell ref="C10:AG10"/>
-    <mergeCell ref="B12:AG12"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:AG13"/>
+    <mergeCell ref="C11:AG11"/>
+    <mergeCell ref="B13:AG13"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="I14:N14"/>
     <mergeCell ref="O14:AG14"/>
@@ -4374,10 +4492,12 @@
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="I23:N23"/>
     <mergeCell ref="O23:AG23"/>
-    <mergeCell ref="B25:AG25"/>
-    <mergeCell ref="C26:AG26"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="I24:N24"/>
+    <mergeCell ref="O24:AG24"/>
+    <mergeCell ref="B26:AG26"/>
     <mergeCell ref="C27:AG27"/>
-    <mergeCell ref="B28:AG28"/>
+    <mergeCell ref="C28:AG28"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
